--- a/Airlines-Services/trajectory/management/commands/SidStar/STAR-LFPG-LUKIP-08L.xlsx
+++ b/Airlines-Services/trajectory/management/commands/SidStar/STAR-LFPG-LUKIP-08L.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rober\git\flight-profile\trajectory\management\commands\SidStar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rober\git\Airlines-Services\Airlines-Services\trajectory\management\commands\SidStar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{945FBB23-9C74-4561-8622-5C44B822FB8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F638C464-3631-4D12-B4C2-A0331B24277A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1140" windowWidth="19200" windowHeight="11170" xr2:uid="{E599D276-CC0B-4999-86A2-09540BAD0A64}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{E599D276-CC0B-4999-86A2-09540BAD0A64}"/>
   </bookViews>
   <sheets>
     <sheet name="WayPoints" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="35">
   <si>
     <t>order</t>
   </si>
@@ -122,22 +122,25 @@
     <t>E003°04'27.80"</t>
   </si>
   <si>
-    <t>LIZY-SUR-OURCQ</t>
-  </si>
-  <si>
     <t>CROUY-SUR-OURCQ</t>
   </si>
   <si>
-    <t>N49°01'06.00"</t>
-  </si>
-  <si>
-    <t>E003°01'00.00"</t>
-  </si>
-  <si>
-    <t>LA-FERTE-MILON</t>
-  </si>
-  <si>
-    <t>CREPY-EN-VALOIS</t>
+    <t>CREPY_EN_VALOIS</t>
+  </si>
+  <si>
+    <t>LA_FERTE_MILON</t>
+  </si>
+  <si>
+    <t>CROUY_SUR_OURCQ</t>
+  </si>
+  <si>
+    <t>PLESSIS_EVEQUE</t>
+  </si>
+  <si>
+    <t>N49°00'25.00"</t>
+  </si>
+  <si>
+    <t>E002°47'23.00"</t>
   </si>
 </sst>
 </file>
@@ -193,9 +196,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -233,7 +236,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -339,7 +342,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -481,7 +484,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -586,7 +589,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
         <v>22</v>
@@ -606,7 +609,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
@@ -626,7 +629,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
         <v>26</v>
@@ -638,7 +641,7 @@
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -646,19 +649,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
